--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfo.xlsx
@@ -1160,6 +1160,28 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+22</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+26</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 M3:M1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfo.xlsx
@@ -14,30 +14,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>退款单号</t>
-  </si>
-  <si>
-    <t>退货单号</t>
-  </si>
-  <si>
-    <t>原订单号</t>
-  </si>
-  <si>
-    <t>平台名称</t>
-  </si>
-  <si>
-    <t>店铺名称</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>退货数量</t>
-  </si>
-  <si>
-    <t>退货金额</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>*退货单号</t>
+  </si>
+  <si>
+    <t>*原订单号</t>
+  </si>
+  <si>
+    <t>*平台名称</t>
+  </si>
+  <si>
+    <t>*店铺名称</t>
+  </si>
+  <si>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*退货数量</t>
+  </si>
+  <si>
+    <t>*退货金额</t>
   </si>
   <si>
     <t>汇率</t>
@@ -46,21 +43,18 @@
     <t>结算汇率</t>
   </si>
   <si>
-    <t>退货状态</t>
-  </si>
-  <si>
-    <t>退货时间</t>
-  </si>
-  <si>
-    <t>原订单时间</t>
+    <t>*退货状态</t>
+  </si>
+  <si>
+    <t>*退货时间</t>
+  </si>
+  <si>
+    <t>*币种</t>
   </si>
   <si>
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.refundId}</t>
-  </si>
-  <si>
     <t>{.returnOrderId}</t>
   </si>
   <si>
@@ -94,7 +88,7 @@
     <t>{.returnCreateTime}</t>
   </si>
   <si>
-    <t>{.orderTime}</t>
+    <t>{.currencyCode}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1068,10 +1062,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:14">
+    <row r="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1105,81 +1099,78 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I1048576">
+  <dataValidations count="6">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:I2 I3:I1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 K3:K1048576 L3:L1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+26</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+22</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999990000</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+26</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 M3:M1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"待处理,已退款,已重发,已完成,已作废"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfo.xlsx
@@ -55,7 +55,7 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.returnOrderId}</t>
+    <t>{.returnOrderCode}</t>
   </si>
   <si>
     <t>{.platformOrderId}</t>
